--- a/out/目次doc.xlsx
+++ b/out/目次doc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D8BDE54-67E9-4107-B1F5-97E8ADB8396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06E1185F-2C54-4D57-BD67-EF33A48021B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6130" yWindow="880" windowWidth="19040" windowHeight="12700" xr2:uid="{8A041000-BECC-47AC-BC3E-7123AE64336F}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="23840" windowHeight="12700" xr2:uid="{DA322864-01FD-43F7-8B78-CC49DB87AEE9}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -171,7 +171,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{3D57D1E7-1385-4A24-82B5-D5E8AAFAFB5C}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{538BF961-0150-4B5C-8723-D1D338DAD6AB}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -502,7 +502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF0179B-B454-43ED-B374-E9C83EDE9E16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE18F537-1A04-4988-A00C-491508C024A4}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/out/目次doc.xlsx
+++ b/out/目次doc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06E1185F-2C54-4D57-BD67-EF33A48021B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20840ADA-EF09-4DED-9D91-D59F7163F573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="23840" windowHeight="12700" xr2:uid="{DA322864-01FD-43F7-8B78-CC49DB87AEE9}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="23840" windowHeight="12700" xr2:uid="{8EF72297-050D-486F-94E7-B1DCE671F0AF}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -171,7 +171,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{538BF961-0150-4B5C-8723-D1D338DAD6AB}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{23BE08B6-130E-4823-82CB-CA9F961B9FF1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -502,7 +502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE18F537-1A04-4988-A00C-491508C024A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D837D5D-48F2-4ABB-B3D7-BFAE56177648}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
